--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129727049</v>
+        <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>57953</v>
+        <v>83341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,41 +1056,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grötomsbodarna, Jmt</t>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501380</v>
+        <v>501350</v>
       </c>
       <c r="R5" t="n">
-        <v>7036996</v>
+        <v>7037029</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1114,17 +1110,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål i döende gran</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,36 +1127,473 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Produktiv, örtfattig och gammal gransumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Persson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136651574</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136651560</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501311</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036880</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Örtrik och högproduktiv grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651560</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136651565</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501345</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7037018</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Produktiv, örtfattig och gammal gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651565</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129727049</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grötomsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501380</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036996</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål i döende gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129727049</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136651578</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99342</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Naturskog öster om Trångbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501234</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7036969</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Örtrik, naturskogsartad granskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136651578</t>
         </is>
       </c>
     </row>
@@ -1175,6 +1603,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38334-2023 artfynd.xlsx
+++ b/artfynd/A 38334-2023 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136651574</v>
       </c>
       <c r="B5" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>136651560</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>136651565</v>
       </c>
       <c r="B7" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>136651578</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
